--- a/ig/main/ValueSet-jdv-j304-finess-statut-juridique-finess.xlsx
+++ b/ig/main/ValueSet-jdv-j304-finess-statut-juridique-finess.xlsx
@@ -7,14 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Exclude #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Expansion Parameters" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="176">
   <si>
     <t>Property</t>
   </si>
@@ -67,15 +67,12 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T12:00:00.000+00:00</t>
+    <t>2026-05-29T09:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
-  </si>
-  <si>
     <t>Jurisdiction</t>
   </si>
   <si>
@@ -85,9 +82,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Ce JDV comporte tous les status juridiques hors agrégat (JDV créé à l'image de l'ancienne TRE_R72-FinessStatutJuridique)</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -100,31 +94,454 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>niveau</t>
-  </si>
-  <si>
-    <t>=</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r400-finess-statut-juridique|20260223120000</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r400-finess-statut-juridique</t>
   </si>
   <si>
-    <t>specialisationRpps</t>
-  </si>
-  <si>
-    <t>true</t>
+    <t>62</t>
+  </si>
+  <si>
+    <t>Association de Droit Local</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Association Loi 1901 non Reconnue d'Utilité Publique</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>Association Loi 1901 Reconnue d'Utilité Publique</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>Assurance Mutuelle Agricole</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Autre Collectivité Territoriale</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Autre Etablissement Public à Caractère Administratif</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>Autre Organisme Mutualiste</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>Autre Organisme Privé à But non Lucratif</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>Autre Organisme Privé à Caractère Commercial</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>Autre Régime de Prévoyance Sociale</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>Autre Société</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Caisse des Ecoles</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Centre Communal d'Action Sociale</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>Centre Intercommunal d'Action Sociale</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Comité d'Entreprise ou Comité d'Etablissement</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>Commune</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>Congrégation</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>Département</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>Entreprise Unipersonnelle Responsabilité Limitée (E.U.R.L.)</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Etablissement Public Communal d'Hospitalisation</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Etablissement Public Départemental d'Hospitalisation</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Etablissement Public Intercommunal d'Hospitalisation</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Etablissement Public Interdépartemental d'Hospitalisation</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Etablissement Public National d'Hospitalisation</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Etablissement Public Régional d'Hospitalisation</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Etablissement Public à Caractère Industriel ou Commercial</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Etablissement Social et Médico-Social Communal</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Etablissement Social et Médico-Social Départemental</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Etablissement Social et Médico-Social Intercommunal</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Etablissement Social et Médico-Social Interdépartemental</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Etablissement Social et Médico-Social National</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Etablissement Social et Médico-Social Régional</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Etat</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>Fondation</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>Groupement d'Intérêt Economique (G.I.E.)</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Groupement d'Intérêt Public (G.I.P.)</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>Groupement de Coopération Sanitaire Privé</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Groupement de Coopération Sanitaire public</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>Groupement de Coopération Sociale ou Médico-Sociale privé</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Groupement de Coopération Sociale ou Médico-Sociale public</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Institution de Prévoyance</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Mutualité Sociale Agricole (M.S.A.)</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>Métropole ou pôle métropolitain</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Office Public d'H.L.M.</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>Organisme de Droit Etranger</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>Personne Physique</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Régime Général de Sécurité Sociale</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Régime Maladie des non Salariés non Agricole</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Régime Spécial de Sécurité Sociale</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>Régime Vieillesse Particulier</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Région</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>Soc. Exercice Libéral Responsabilité Limitée (S.E.L.A.R.L.)</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>Société A Responsabilité Limitée (S.A.R.L.)</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>Société Anonyme (S.A.)</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>Société Civile</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>Société Civile de Moyens (S.C.M.)</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>Société Civile Professionnelle (S.C.P.)</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>Société d'Exercice Libéral à Forme Anonyme (S.E.L.A.F.A.)</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>Société en commandite</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>Société en Nom Collectif (S.N.C.)</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>Société Exercice Libéral Commandite par Actions (S.E.L.C.A.)</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>Société Exercice Libéral par Actions Simplifiée (S.E.L.A.S.)</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>Société Interprofessionnelle Soins Ambulatoires (S.I.S.A.)</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>Société Mutualiste</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>Société par Actions Simplifiée (S.A.S.)</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>Syndicat</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>Syndicat de Propriétaires</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Syndicat Inter Hospitalier</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>Territoire d'Outre Mer</t>
   </si>
 </sst>
 </file>
@@ -341,44 +758,40 @@
       <c r="A10" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
-      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -388,49 +801,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="C1" t="s" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -440,49 +835,1479 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>32</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>35</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E49" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E50" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E51" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E52" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E53" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E54" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="F54" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="E55" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="F55" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E56" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="F56" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E57" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="E58" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="F58" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="E59" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="F59" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="E60" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="F60" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E61" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="F61" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="E62" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="F62" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E63" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="F63" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E64" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="F64" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E65" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="F65" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="E66" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="F66" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="E67" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F67" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="E68" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="F68" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="E69" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="F69" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="E70" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="F70" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-jdv-j304-finess-statut-juridique-finess.xlsx
+++ b/ig/main/ValueSet-jdv-j304-finess-statut-juridique-finess.xlsx
@@ -9,12 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Exclude #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Expansion Parameters" r:id="rId6" sheetId="4"/>
+    <sheet name="Expansion" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="186">
   <si>
     <t>Property</t>
   </si>
@@ -125,6 +127,453 @@
   </si>
   <si>
     <t>true</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r400-finess-statut-juridique|20260223120000</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>Association de Droit Local</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Association Loi 1901 non Reconnue d'Utilité Publique</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>Association Loi 1901 Reconnue d'Utilité Publique</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>Assurance Mutuelle Agricole</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Autre Collectivité Territoriale</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Autre Etablissement Public à Caractère Administratif</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>Autre Organisme Mutualiste</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>Autre Organisme Privé à But non Lucratif</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>Autre Organisme Privé à Caractère Commercial</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>Autre Régime de Prévoyance Sociale</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>Autre Société</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Caisse des Ecoles</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Centre Communal d'Action Sociale</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>Centre Intercommunal d'Action Sociale</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Comité d'Entreprise ou Comité d'Etablissement</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>Commune</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>Congrégation</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>Département</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>Entreprise Unipersonnelle Responsabilité Limitée (E.U.R.L.)</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Etablissement Public Communal d'Hospitalisation</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Etablissement Public Départemental d'Hospitalisation</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Etablissement Public Intercommunal d'Hospitalisation</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Etablissement Public Interdépartemental d'Hospitalisation</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Etablissement Public National d'Hospitalisation</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Etablissement Public Régional d'Hospitalisation</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Etablissement Public à Caractère Industriel ou Commercial</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Etablissement Social et Médico-Social Communal</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Etablissement Social et Médico-Social Départemental</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Etablissement Social et Médico-Social Intercommunal</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Etablissement Social et Médico-Social Interdépartemental</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Etablissement Social et Médico-Social National</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Etablissement Social et Médico-Social Régional</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Etat</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>Fondation</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>Groupement d'Intérêt Economique (G.I.E.)</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Groupement d'Intérêt Public (G.I.P.)</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>Groupement de Coopération Sanitaire Privé</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Groupement de Coopération Sanitaire public</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>Groupement de Coopération Sociale ou Médico-Sociale privé</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Groupement de Coopération Sociale ou Médico-Sociale public</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Institution de Prévoyance</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Mutualité Sociale Agricole (M.S.A.)</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>Métropole ou pôle métropolitain</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Office Public d'H.L.M.</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>Organisme de Droit Etranger</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>Personne Physique</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Régime Général de Sécurité Sociale</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Régime Maladie des non Salariés non Agricole</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Régime Spécial de Sécurité Sociale</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>Régime Vieillesse Particulier</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Région</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>Soc. Exercice Libéral Responsabilité Limitée (S.E.L.A.R.L.)</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>Société A Responsabilité Limitée (S.A.R.L.)</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>Société Anonyme (S.A.)</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>Société Civile</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>Société Civile de Moyens (S.C.M.)</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>Société Civile Professionnelle (S.C.P.)</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>Société d'Exercice Libéral à Forme Anonyme (S.E.L.A.F.A.)</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>Société en commandite</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>Société en Nom Collectif (S.N.C.)</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>Société Exercice Libéral Commandite par Actions (S.E.L.C.A.)</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>Société Exercice Libéral par Actions Simplifiée (S.E.L.A.S.)</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>Société Interprofessionnelle Soins Ambulatoires (S.I.S.A.)</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>Société Mutualiste</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>Société par Actions Simplifiée (S.A.S.)</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>Syndicat</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>Syndicat de Propriétaires</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Syndicat Inter Hospitalier</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>Territoire d'Outre Mer</t>
   </si>
 </sst>
 </file>
@@ -488,4 +937,1520 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G70"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>44</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E49" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="E50" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E51" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E52" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="E53" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="E54" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="F54" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="E55" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="F55" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E56" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="F56" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="E57" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E58" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="F58" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E59" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="F59" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E60" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="F60" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="E61" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="F61" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="E62" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F62" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="E63" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="F63" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="E64" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="F64" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="E65" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="F65" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="E66" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="F66" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="E67" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="F67" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E68" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="F68" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="E69" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="F69" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="E70" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="F70" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ig/main/ValueSet-jdv-j304-finess-statut-juridique-finess.xlsx
+++ b/ig/main/ValueSet-jdv-j304-finess-statut-juridique-finess.xlsx
@@ -135,7 +135,7 @@
     <t>used-codesystem</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r400-finess-statut-juridique|20260223120000</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r400-finess-statut-juridique|20260629120000</t>
   </si>
   <si>
     <t>version</t>
